--- a/r4-core-157-add-vbpk-as-patientidentifier/StructureDefinition-at-core-ext-gender-administrativeGenderAddition.xlsx
+++ b/r4-core-157-add-vbpk-as-patientidentifier/StructureDefinition-at-core-ext-gender-administrativeGenderAddition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T08:37:32+00:00</t>
+    <t>2026-04-30T08:59:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-157-add-vbpk-as-patientidentifier/StructureDefinition-at-core-ext-gender-administrativeGenderAddition.xlsx
+++ b/r4-core-157-add-vbpk-as-patientidentifier/StructureDefinition-at-core-ext-gender-administrativeGenderAddition.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-ext-gender-administrativeGenderAddition</t>
+    <t>https://fhir.hl7.at/core/r4/StructureDefinition/at-core-ext-gender-administrativeGenderAddition</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T08:59:13+00:00</t>
+    <t>2026-08-21T10:22:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -148,13 +148,13 @@
     <t>element:Person.gender</t>
   </si>
   <si>
-    <t>element:http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient#Patient.gender</t>
-  </si>
-  <si>
-    <t>element:http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient#Patient.contact.gender</t>
-  </si>
-  <si>
-    <t>element:http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner#Practitioner.gender</t>
+    <t>element:https://fhir.hl7.at/core/r4/StructureDefinition/at-core-patient#Patient.gender</t>
+  </si>
+  <si>
+    <t>element:https://fhir.hl7.at/core/r4/StructureDefinition/at-core-patient#Patient.contact.gender</t>
+  </si>
+  <si>
+    <t>element:https://fhir.hl7.at/core/r4/StructureDefinition/at-core-practitioner#Practitioner.gender</t>
   </si>
   <si>
     <t>ID</t>
